--- a/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0003T0006Z000C1N38_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0003T0006Z000C1N38_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>58.86218411703907</v>
+        <v>9.56510491901885</v>
       </c>
       <c r="D2" t="n">
-        <v>50.09541548118569</v>
+        <v>8.140505015692675</v>
       </c>
       <c r="E2" t="n">
-        <v>13.68625991844001</v>
+        <v>2.224017236746502</v>
       </c>
       <c r="F2" t="n">
-        <v>14.23851773884283</v>
+        <v>2.31375913256196</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>58.25733187217681</v>
+        <v>9.466816429228732</v>
       </c>
       <c r="D3" t="n">
-        <v>49.30215095216439</v>
+        <v>8.011599529726714</v>
       </c>
       <c r="E3" t="n">
-        <v>13.68625991844001</v>
+        <v>2.224017236746502</v>
       </c>
       <c r="F3" t="n">
-        <v>14.23851773884283</v>
+        <v>2.31375913256196</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>34.22706281698106</v>
+        <v>5.561897707759423</v>
       </c>
       <c r="D4" t="n">
-        <v>33.73689764882418</v>
+        <v>5.482245867933929</v>
       </c>
       <c r="E4" t="n">
-        <v>13.68625991844001</v>
+        <v>2.224017236746502</v>
       </c>
       <c r="F4" t="n">
-        <v>14.23851773884283</v>
+        <v>2.31375913256196</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>52.77978440270604</v>
+        <v>8.576714965439733</v>
       </c>
       <c r="D5" t="n">
-        <v>10.92331264391644</v>
+        <v>1.775038304636421</v>
       </c>
       <c r="E5" t="n">
-        <v>13.68625991844001</v>
+        <v>2.224017236746502</v>
       </c>
       <c r="F5" t="n">
-        <v>14.23851773884283</v>
+        <v>2.31375913256196</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>23.74766033859938</v>
+        <v>3.858994805022399</v>
       </c>
       <c r="D6" t="n">
-        <v>14.82157251017683</v>
+        <v>2.408505532903735</v>
       </c>
       <c r="E6" t="n">
-        <v>13.68625991844001</v>
+        <v>2.224017236746502</v>
       </c>
       <c r="F6" t="n">
-        <v>14.23851773884283</v>
+        <v>2.31375913256196</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>48.63864850677125</v>
+        <v>7.903780382350329</v>
       </c>
       <c r="D7" t="n">
-        <v>6.182010289909289</v>
+        <v>1.004576672110259</v>
       </c>
       <c r="E7" t="n">
-        <v>13.68625991844001</v>
+        <v>2.224017236746502</v>
       </c>
       <c r="F7" t="n">
-        <v>14.23851773884283</v>
+        <v>2.31375913256196</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>32.16164878562317</v>
+        <v>5.226267927663765</v>
       </c>
       <c r="D8" t="n">
-        <v>32.16283427378185</v>
+        <v>5.226460569489552</v>
       </c>
       <c r="E8" t="n">
-        <v>13.68625991844001</v>
+        <v>2.224017236746502</v>
       </c>
       <c r="F8" t="n">
-        <v>14.23851773884283</v>
+        <v>2.31375913256196</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>36.15332248516015</v>
+        <v>5.874914903838524</v>
       </c>
       <c r="D9" t="n">
-        <v>6.943751728089139</v>
+        <v>1.128359655814485</v>
       </c>
       <c r="E9" t="n">
-        <v>13.68625991844001</v>
+        <v>2.224017236746502</v>
       </c>
       <c r="F9" t="n">
-        <v>14.23851773884283</v>
+        <v>2.31375913256196</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>26.06620810933879</v>
+        <v>4.235758817767553</v>
       </c>
       <c r="D10" t="n">
-        <v>26.34235664844839</v>
+        <v>4.280632955372863</v>
       </c>
       <c r="E10" t="n">
-        <v>13.68625991844001</v>
+        <v>2.224017236746502</v>
       </c>
       <c r="F10" t="n">
-        <v>14.23851773884283</v>
+        <v>2.31375913256196</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>22.26657456536027</v>
+        <v>3.618318366871044</v>
       </c>
       <c r="D11" t="n">
-        <v>20.11642678036459</v>
+        <v>3.268919351809246</v>
       </c>
       <c r="E11" t="n">
-        <v>13.68625991844001</v>
+        <v>2.224017236746502</v>
       </c>
       <c r="F11" t="n">
-        <v>14.23851773884283</v>
+        <v>2.31375913256196</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>29.55223856170251</v>
+        <v>4.802238766276658</v>
       </c>
       <c r="D12" t="n">
-        <v>23.84806654170895</v>
+        <v>3.875310813027705</v>
       </c>
       <c r="E12" t="n">
-        <v>13.68625991844001</v>
+        <v>2.224017236746502</v>
       </c>
       <c r="F12" t="n">
-        <v>14.23851773884283</v>
+        <v>2.31375913256196</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>35.53537445911545</v>
+        <v>5.774498349606262</v>
       </c>
       <c r="D13" t="n">
-        <v>6.147019876549857</v>
+        <v>0.9988907299393518</v>
       </c>
       <c r="E13" t="n">
-        <v>13.68625991844001</v>
+        <v>2.224017236746502</v>
       </c>
       <c r="F13" t="n">
-        <v>14.23851773884283</v>
+        <v>2.31375913256196</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>13.5002525179738</v>
+        <v>2.193791034170743</v>
       </c>
       <c r="D14" t="n">
-        <v>7.015371130508029</v>
+        <v>1.139997808707555</v>
       </c>
       <c r="E14" t="n">
-        <v>13.68625991844001</v>
+        <v>2.224017236746502</v>
       </c>
       <c r="F14" t="n">
-        <v>14.23851773884283</v>
+        <v>2.31375913256196</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>33.1887636404161</v>
+        <v>5.393174091567616</v>
       </c>
       <c r="D15" t="n">
-        <v>9.668326190649585</v>
+        <v>1.571103005980558</v>
       </c>
       <c r="E15" t="n">
-        <v>13.68625991844001</v>
+        <v>2.224017236746502</v>
       </c>
       <c r="F15" t="n">
-        <v>14.23851773884283</v>
+        <v>2.31375913256196</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>18.59799652557973</v>
+        <v>3.022174435406707</v>
       </c>
       <c r="D16" t="n">
-        <v>8.234955997948438</v>
+        <v>1.338180349666621</v>
       </c>
       <c r="E16" t="n">
-        <v>13.68625991844001</v>
+        <v>2.224017236746502</v>
       </c>
       <c r="F16" t="n">
-        <v>14.23851773884283</v>
+        <v>2.31375913256196</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>18.84710680620453</v>
+        <v>3.062654856008236</v>
       </c>
       <c r="D17" t="n">
-        <v>16.57339455108283</v>
+        <v>2.693176614550961</v>
       </c>
       <c r="E17" t="n">
-        <v>13.68625991844001</v>
+        <v>2.224017236746502</v>
       </c>
       <c r="F17" t="n">
-        <v>14.23851773884283</v>
+        <v>2.31375913256196</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
